--- a/data/trans_orig/P1410-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2007</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11787</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>38628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439205</t>
+          <t>439546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459379</t>
+          <t>459276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294893</t>
+          <t>295700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305610</t>
+          <t>305537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740085</t>
+          <t>741829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762084</t>
+          <t>762793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20167</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346767</t>
+          <t>346169</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360342</t>
+          <t>360206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>358818</t>
+          <t>356310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369781</t>
+          <t>369747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710136</t>
+          <t>711301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727996</t>
+          <t>727722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39468</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505466</t>
+          <t>505348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525363</t>
+          <t>524731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159017</t>
+          <t>158882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166848</t>
+          <t>166842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>670703</t>
+          <t>669753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690364</t>
+          <t>690466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57606</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90442</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78686</t>
+          <t>77887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117171</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1147892</t>
+          <t>1149153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1180728</t>
+          <t>1182299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678438</t>
+          <t>677319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697000</t>
+          <t>697775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835449</t>
+          <t>1837286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1873934</t>
+          <t>1874733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28856</t>
+          <t>27281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>35006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>61593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321699</t>
+          <t>323274</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338931</t>
+          <t>339688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528724</t>
+          <t>528621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>549659</t>
+          <t>550101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>857619</t>
+          <t>857714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884570</t>
+          <t>884301</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4587</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77824</t>
+          <t>75440</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47638</t>
+          <t>46238</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1170936</t>
+          <t>1173320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1202713</t>
+          <t>1202574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1470393</t>
+          <t>1469523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1499322</t>
+          <t>1500722</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128761</t>
+          <t>129367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175137</t>
+          <t>175840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104900</t>
+          <t>106668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147352</t>
+          <t>150257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245992</t>
+          <t>244451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310680</t>
+          <t>311527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3095053</t>
+          <t>3094350</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3141429</t>
+          <t>3140823</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3230772</t>
+          <t>3227867</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3273224</t>
+          <t>3271456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6337634</t>
+          <t>6336787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6402322</t>
+          <t>6403863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2012</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>418750</t>
+          <t>417944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431411</t>
+          <t>431336</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309386</t>
+          <t>308594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730874</t>
+          <t>731421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>744715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397649</t>
+          <t>397539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413574</t>
+          <t>413289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327094</t>
+          <t>327485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337038</t>
+          <t>337029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728588</t>
+          <t>731096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748122</t>
+          <t>747983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19739</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29046</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>53829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>587255</t>
+          <t>585393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609676</t>
+          <t>608008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242727</t>
+          <t>242555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255259</t>
+          <t>255054</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835706</t>
+          <t>835715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860498</t>
+          <t>860336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69184</t>
+          <t>66380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53557</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>88021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1089825</t>
+          <t>1092629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1120101</t>
+          <t>1121686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738911</t>
+          <t>739254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754540</t>
+          <t>754666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1837750</t>
+          <t>1835710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1870174</t>
+          <t>1871437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>15029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38201</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65649</t>
+          <t>67390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59037</t>
+          <t>58906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>95258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>474828</t>
+          <t>476373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>494786</t>
+          <t>495567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694597</t>
+          <t>692856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722045</t>
+          <t>720849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1177983</t>
+          <t>1175585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1211806</t>
+          <t>1211937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50943</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83792</t>
+          <t>82700</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54728</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89340</t>
+          <t>88294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254627</t>
+          <t>253646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265919</t>
+          <t>265912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1024377</t>
+          <t>1025469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1057226</t>
+          <t>1057153</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1285711</t>
+          <t>1286757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1320323</t>
+          <t>1321246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>111966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155278</t>
+          <t>157398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124875</t>
+          <t>124063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173933</t>
+          <t>172280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250117</t>
+          <t>247688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312544</t>
+          <t>313079</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3266632</t>
+          <t>3264512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3311645</t>
+          <t>3309944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3371799</t>
+          <t>3373452</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3420857</t>
+          <t>3421669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6655098</t>
+          <t>6654563</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6717525</t>
+          <t>6719954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2016</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22406</t>
+          <t>22357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17127</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407334</t>
+          <t>406093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422287</t>
+          <t>422269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324649</t>
+          <t>324698</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339567</t>
+          <t>339541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738929</t>
+          <t>737407</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759020</t>
+          <t>758755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13211</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30985</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356066</t>
+          <t>355119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370518</t>
+          <t>370379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359062</t>
+          <t>359484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370077</t>
+          <t>369873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718515</t>
+          <t>720410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736974</t>
+          <t>738031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32534</t>
+          <t>33598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23668</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489380</t>
+          <t>488316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507879</t>
+          <t>506835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145576</t>
+          <t>143845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160837</t>
+          <t>159813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640347</t>
+          <t>639942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>664368</t>
+          <t>663525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66594</t>
+          <t>66537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57762</t>
+          <t>57594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91174</t>
+          <t>93532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1083044</t>
+          <t>1083101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1110819</t>
+          <t>1110496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>788903</t>
+          <t>792048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811239</t>
+          <t>811777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884340</t>
+          <t>1881982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917752</t>
+          <t>1917920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>45591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>75866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582676</t>
+          <t>582486</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602521</t>
+          <t>603179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>693905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716527</t>
+          <t>715879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283805</t>
+          <t>1283084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1314077</t>
+          <t>1313359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57357</t>
+          <t>57464</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91899</t>
+          <t>94597</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57371</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94788</t>
+          <t>93648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281162</t>
+          <t>281212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>990126</t>
+          <t>987428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024668</t>
+          <t>1024561</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1274382</t>
+          <t>1275522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1311799</t>
+          <t>1312462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105533</t>
+          <t>106371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>149414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132284</t>
+          <t>132664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186333</t>
+          <t>187778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>256910</t>
+          <t>253321</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322907</t>
+          <t>321169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3232506</t>
+          <t>3236308</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3280189</t>
+          <t>3279351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3345263</t>
+          <t>3343818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3399312</t>
+          <t>3398932</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6594411</t>
+          <t>6596149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6660408</t>
+          <t>6663997</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos cardíacos en 2023</t>
+          <t>Población con diagnóstico de trastornos cardíacos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>33470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47777</t>
+          <t>48063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471180</t>
+          <t>471742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487992</t>
+          <t>488434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427210</t>
+          <t>428138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439474</t>
+          <t>439802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904902</t>
+          <t>904616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924668</t>
+          <t>924751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425313</t>
+          <t>424634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439528</t>
+          <t>439756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373106</t>
+          <t>372742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379717</t>
+          <t>379662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>801527</t>
+          <t>801763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>817394</t>
+          <t>817418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>48389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>14786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618426</t>
+          <t>619156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656071</t>
+          <t>657850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147141</t>
+          <t>146819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160990</t>
+          <t>160851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>776150</t>
+          <t>777221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820823</t>
+          <t>819670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>51190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>78919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>61696</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103578</t>
+          <t>103758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>953096</t>
+          <t>954580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981489</t>
+          <t>982309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948013</t>
+          <t>948038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968322</t>
+          <t>968489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907428</t>
+          <t>1907248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951894</t>
+          <t>1949310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24326</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44230</t>
+          <t>43613</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>33972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57780</t>
+          <t>57572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63694</t>
+          <t>61754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94917</t>
+          <t>94643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429819</t>
+          <t>430436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>449723</t>
+          <t>449946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>779990</t>
+          <t>780198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>805084</t>
+          <t>803798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1216902</t>
+          <t>1217176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248125</t>
+          <t>1250065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>24191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64537</t>
+          <t>64408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>46318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74172</t>
+          <t>75489</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210329</t>
+          <t>216316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239996</t>
+          <t>239990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>695757</t>
+          <t>695886</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>717009</t>
+          <t>717181</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>926629</t>
+          <t>925312</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953874</t>
+          <t>954483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>137503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201373</t>
+          <t>201341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115617</t>
+          <t>120652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>167655</t>
+          <t>169500</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>272308</t>
+          <t>276997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>361024</t>
+          <t>360007</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3171652</t>
+          <t>3171684</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3239524</t>
+          <t>3235522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3404206</t>
+          <t>3402361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3456244</t>
+          <t>3451209</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6583861</t>
+          <t>6584878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6672577</t>
+          <t>6667888</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1410-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1410-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>18167</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38628</t>
+          <t>39555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>439546</t>
+          <t>440569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459276</t>
+          <t>459027</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295700</t>
+          <t>295557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305537</t>
+          <t>305549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>741829</t>
+          <t>740902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762793</t>
+          <t>762290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27498</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346169</t>
+          <t>346572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360206</t>
+          <t>360014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356310</t>
+          <t>358033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369747</t>
+          <t>369535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711301</t>
+          <t>710868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727722</t>
+          <t>727793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40418</t>
+          <t>39924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505348</t>
+          <t>505876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524731</t>
+          <t>524406</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158882</t>
+          <t>158857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166842</t>
+          <t>166843</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669753</t>
+          <t>670247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690466</t>
+          <t>690421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>87924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36966</t>
+          <t>36326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77887</t>
+          <t>78632</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>115100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1149153</t>
+          <t>1150410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1182299</t>
+          <t>1182580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>677319</t>
+          <t>677959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697775</t>
+          <t>697882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1837286</t>
+          <t>1837520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1874733</t>
+          <t>1873988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35006</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61593</t>
+          <t>62114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323274</t>
+          <t>323066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339688</t>
+          <t>339697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528621</t>
+          <t>527892</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550101</t>
+          <t>549681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>857714</t>
+          <t>857193</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884301</t>
+          <t>884670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>47143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75440</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77437</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1173320</t>
+          <t>1172728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1202574</t>
+          <t>1201617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1469523</t>
+          <t>1469238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1500722</t>
+          <t>1499118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129367</t>
+          <t>127597</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175840</t>
+          <t>174915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106668</t>
+          <t>105408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150257</t>
+          <t>151712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244451</t>
+          <t>246206</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>311527</t>
+          <t>310173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3094350</t>
+          <t>3095275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3140823</t>
+          <t>3142593</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3227867</t>
+          <t>3226412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3271456</t>
+          <t>3272716</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6336787</t>
+          <t>6338141</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6403863</t>
+          <t>6402108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417944</t>
+          <t>417976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431336</t>
+          <t>431346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308594</t>
+          <t>308846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731421</t>
+          <t>730890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744715</t>
+          <t>744820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21258</t>
+          <t>20673</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397539</t>
+          <t>398124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413289</t>
+          <t>413582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327485</t>
+          <t>327284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337029</t>
+          <t>337044</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731096</t>
+          <t>731608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747983</t>
+          <t>748469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44022</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>53539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585393</t>
+          <t>586925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608008</t>
+          <t>608665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242555</t>
+          <t>242749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255054</t>
+          <t>255574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835715</t>
+          <t>836005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860336</t>
+          <t>860981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37323</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66380</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88021</t>
+          <t>85906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1092629</t>
+          <t>1090302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1121686</t>
+          <t>1120583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739254</t>
+          <t>739393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754666</t>
+          <t>755444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835710</t>
+          <t>1837825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1871437</t>
+          <t>1873194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>34626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67390</t>
+          <t>65828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58906</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95258</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>476373</t>
+          <t>475970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495567</t>
+          <t>495409</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>692856</t>
+          <t>694418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720849</t>
+          <t>722229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1175585</t>
+          <t>1178798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1211937</t>
+          <t>1212803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>82707</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>53892</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>87393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253646</t>
+          <t>253389</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265912</t>
+          <t>265919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1025469</t>
+          <t>1025462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1057153</t>
+          <t>1056954</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1286757</t>
+          <t>1287658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1321246</t>
+          <t>1321159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>111966</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157398</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124063</t>
+          <t>123751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172280</t>
+          <t>171396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247688</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313079</t>
+          <t>314144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3264512</t>
+          <t>3266976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3309944</t>
+          <t>3312483</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3373452</t>
+          <t>3374336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3421669</t>
+          <t>3421981</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6654563</t>
+          <t>6653498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6719954</t>
+          <t>6720688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22999</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>22457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>39589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406093</t>
+          <t>406120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422269</t>
+          <t>422376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324698</t>
+          <t>324598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339541</t>
+          <t>339338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737407</t>
+          <t>736558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758755</t>
+          <t>758492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355119</t>
+          <t>355967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>370379</t>
+          <t>369843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359484</t>
+          <t>359741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369873</t>
+          <t>370022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720410</t>
+          <t>718288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>738031</t>
+          <t>737485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33598</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22278</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>48365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488316</t>
+          <t>488900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506835</t>
+          <t>506812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143845</t>
+          <t>145027</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159813</t>
+          <t>159990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639942</t>
+          <t>639671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663525</t>
+          <t>663338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66537</t>
+          <t>65547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33828</t>
+          <t>34530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57594</t>
+          <t>57976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93532</t>
+          <t>91942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1083101</t>
+          <t>1084091</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1110496</t>
+          <t>1112033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>792048</t>
+          <t>791346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>811777</t>
+          <t>811456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1881982</t>
+          <t>1883572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1917920</t>
+          <t>1917538</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>21495</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45591</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75866</t>
+          <t>74368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582486</t>
+          <t>583063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603179</t>
+          <t>602279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>693905</t>
+          <t>693710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>715879</t>
+          <t>716749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283084</t>
+          <t>1284582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1313359</t>
+          <t>1313474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57464</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94597</t>
+          <t>91034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>57483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93648</t>
+          <t>94754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281212</t>
+          <t>281168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>987428</t>
+          <t>990991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1024561</t>
+          <t>1027359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1275522</t>
+          <t>1274416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1312462</t>
+          <t>1311687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106371</t>
+          <t>106291</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>149414</t>
+          <t>150464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132664</t>
+          <t>135599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187778</t>
+          <t>186003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253321</t>
+          <t>253264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>321169</t>
+          <t>321884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3236308</t>
+          <t>3235258</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3279351</t>
+          <t>3279431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3343818</t>
+          <t>3345593</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3398932</t>
+          <t>3395997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6596149</t>
+          <t>6595434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6663997</t>
+          <t>6664054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24290</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33470</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36680</t>
+          <t>43074</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>480922</t>
+          <t>521551</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471742</t>
+          <t>510005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>488434</t>
+          <t>529112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>435077</t>
+          <t>474405</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428138</t>
+          <t>467091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439802</t>
+          <t>479737</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>915999</t>
+          <t>995955</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904616</t>
+          <t>984484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924751</t>
+          <t>1006496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27579</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>433357</t>
+          <t>463167</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424634</t>
+          <t>454377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439756</t>
+          <t>469553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>376944</t>
+          <t>417206</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372742</t>
+          <t>412741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>379662</t>
+          <t>420280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,27 +9159,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>810302</t>
+          <t>880373</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>801763</t>
+          <t>871006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>817418</t>
+          <t>887616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>29904</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48389</t>
+          <t>40780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>41539</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640057</t>
+          <t>440839</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619156</t>
+          <t>429963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657850</t>
+          <t>449609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>156659</t>
+          <t>175862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146819</t>
+          <t>164055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160851</t>
+          <t>181137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>796716</t>
+          <t>616702</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>777221</t>
+          <t>602889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819670</t>
+          <t>626709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64361</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>54681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78919</t>
+          <t>84410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>84442</t>
+          <t>89878</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61696</t>
+          <t>74296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103758</t>
+          <t>109218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>969138</t>
+          <t>1061906</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>954580</t>
+          <t>1046052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>982309</t>
+          <t>1075781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>957427</t>
+          <t>839221</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948038</t>
+          <t>831164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968489</t>
+          <t>845299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1926564</t>
+          <t>1901127</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907248</t>
+          <t>1881787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1949310</t>
+          <t>1916709</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033499</t>
+          <t>1130462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033499</t>
+          <t>1130462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033499</t>
+          <t>1130462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977508</t>
+          <t>860543</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977508</t>
+          <t>860543</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977508</t>
+          <t>860543</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011006</t>
+          <t>1991005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011006</t>
+          <t>1991005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011006</t>
+          <t>1991005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,67 +10005,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33175</t>
+          <t>34646</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43613</t>
+          <t>47033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>52311</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>42075</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>63676</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>5,08%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46293</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>33972</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>57572</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61754</t>
+          <t>73110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94643</t>
+          <t>102041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -10118,69 +10118,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>440874</t>
+          <t>532330</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430436</t>
+          <t>519943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>449946</t>
+          <t>541626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>776521</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>765156</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>786757</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
           <t>94,92%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>791477</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>780198</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>803798</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>93,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1688</t>
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1232352</t>
+          <t>1308851</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1217176</t>
+          <t>1293767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250065</t>
+          <t>1322698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837770</t>
+          <t>828832</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837770</t>
+          <t>828832</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837770</t>
+          <t>828832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1311819</t>
+          <t>1395808</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1311819</t>
+          <t>1395808</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1311819</t>
+          <t>1395808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52968</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64408</t>
+          <t>70566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>62406</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75489</t>
+          <t>77807</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235141</t>
+          <t>232598</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216316</t>
+          <t>213527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239990</t>
+          <t>236711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>707326</t>
+          <t>785418</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>695886</t>
+          <t>772629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>717181</t>
+          <t>796404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>942468</t>
+          <t>1018017</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>925312</t>
+          <t>1002616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>954483</t>
+          <t>1030158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>173535</t>
+          <t>186849</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137503</t>
+          <t>160647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201341</t>
+          <t>211193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>146950</t>
+          <t>162337</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120652</t>
+          <t>142071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169500</t>
+          <t>184797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>320485</t>
+          <t>349186</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276997</t>
+          <t>318539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>360007</t>
+          <t>381353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3199490</t>
+          <t>3252391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3171684</t>
+          <t>3228047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3235522</t>
+          <t>3278593</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3424911</t>
+          <t>3468633</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3402361</t>
+          <t>3446173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3451209</t>
+          <t>3488899</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6624400</t>
+          <t>6721023</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6584878</t>
+          <t>6688856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6667888</t>
+          <t>6751670</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373025</t>
+          <t>3439240</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373025</t>
+          <t>3439240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373025</t>
+          <t>3439240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571861</t>
+          <t>3630970</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571861</t>
+          <t>3630970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571861</t>
+          <t>3630970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944885</t>
+          <t>7070209</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944885</t>
+          <t>7070209</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944885</t>
+          <t>7070209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
